--- a/hard/xlsx1.xlsx
+++ b/hard/xlsx1.xlsx
@@ -382,14 +382,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -400,13 +400,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="46.2" x14ac:dyDescent="0.85">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -419,10 +419,19 @@
       <c r="E4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="46.2" x14ac:dyDescent="0.85">
+      <c r="H4" s="1">
+        <v>4444</v>
+      </c>
+      <c r="I4" s="1">
+        <v>2</v>
+      </c>
+      <c r="J4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="46.2" x14ac:dyDescent="0.85">
       <c r="B7" s="1">
-        <v>4444</v>
+        <v>1111</v>
       </c>
       <c r="C7" s="1">
         <v>2</v>
@@ -432,12 +441,15 @@
       </c>
       <c r="E7" s="1"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="46.2" x14ac:dyDescent="0.85">
+      <c r="B11" s="1">
+        <v>4444</v>
+      </c>
       <c r="H11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
         <v>2</v>
       </c>
@@ -445,7 +457,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>2</v>
       </c>
